--- a/media/statement_files/Statement_2025-05-01.xlsx
+++ b/media/statement_files/Statement_2025-05-01.xlsx
@@ -581,7 +581,7 @@
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>151</t>
         </is>
       </c>
       <c r="I9" s="5" t="n"/>
@@ -738,30 +738,22 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>NA24MATR001, NA24PCHR001, NA24PCHR004, NA24PCHR007, NA24PHYR002</t>
+          <t>NA24MATR006, NA24PHYR002, NA24PHYR005, NA24PHYR021, NA24PHYR028</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>NA24PHYR005, NA24PHYR021, NA24PHYR028, NA24PLSR011, NA24PLSR024</t>
+          <t>NA24PLSR011</t>
         </is>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>NA24STAR004, NA24STAR010, NA24STAR014, NA24STAR019, NA24STAR021</t>
-        </is>
-      </c>
+      <c r="A25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>NA24STAR022, NA24ZOOR010, NA24ZOOR018, NA24ZOOR025</t>
-        </is>
-      </c>
+      <c r="A26" s="10" t="inlineStr"/>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="10" t="inlineStr"/>
@@ -1287,7 +1279,7 @@
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>153</t>
         </is>
       </c>
       <c r="I9" s="5" t="n"/>
@@ -1442,7 +1434,11 @@
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="9" t="inlineStr"/>
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>NA24ECOR004, NA24ECOR035</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="10" t="inlineStr"/>
